--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.689368009567261</v>
+        <v>7.303773641586304</v>
       </c>
       <c r="E2" t="n">
         <v>0.9985491167103056</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>7.992323637008667</v>
+        <v>7.486937761306763</v>
       </c>
       <c r="E3" t="n">
         <v>0.9991212652721163</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.689368009567261</v>
+        <v>7.303773641586304</v>
       </c>
       <c r="E2" t="n">
         <v>0.9985491167103056</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>7.992323637008667</v>
+        <v>7.486937761306763</v>
       </c>
       <c r="E3" t="n">
         <v>0.9991212652721163</v>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.303773641586304</v>
+        <v>33.34668922424316</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9985491167103056</v>
+        <v>0.9957603155974105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9995224064768821</v>
+        <v>0.9972056385643899</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4306637610594572</v>
+        <v>1.041718565298485</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3130241899402439</v>
+        <v>0.7294976117107828</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 3, 'n_estimators': 200, 'num_leaves': 31}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
         </is>
       </c>
     </row>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>7.486937761306763</v>
+        <v>39.18174290657043</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9991212652721163</v>
+        <v>0.9965907516726771</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9995446518581431</v>
+        <v>0.9972056385643899</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4205144258328332</v>
+        <v>1.041718565298485</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2735053729299763</v>
+        <v>0.7294976117107828</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.303773641586304</v>
+        <v>33.34668922424316</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9985491167103056</v>
+        <v>0.9957603155974105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9995224064768821</v>
+        <v>0.9972056385643899</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4306637610594572</v>
+        <v>1.041718565298485</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3130241899402439</v>
+        <v>0.7294976117107828</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 3, 'n_estimators': 200, 'num_leaves': 31}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>7.486937761306763</v>
+        <v>39.18174290657043</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9991212652721163</v>
+        <v>0.9965907516726771</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9995446518581431</v>
+        <v>0.9972056385643899</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4205144258328332</v>
+        <v>1.041718565298485</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2735053729299763</v>
+        <v>0.7294976117107828</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>33.34668922424316</v>
+        <v>25.09299921989441</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9957603155974105</v>
+        <v>0.9536975256415268</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9972056385643899</v>
+        <v>0.9604850750997985</v>
       </c>
       <c r="G2" t="n">
-        <v>1.041718565298485</v>
+        <v>35.37310208186549</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7294976117107828</v>
+        <v>21.87717418785341</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>39.18174290657043</v>
+        <v>36.17952656745911</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9965907516726771</v>
+        <v>0.9563953673331633</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9972056385643899</v>
+        <v>0.961021482177699</v>
       </c>
       <c r="G3" t="n">
-        <v>1.041718565298485</v>
+        <v>35.13219036906995</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7294976117107828</v>
+        <v>22.11323101640784</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>74.39666152000427</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9581187558108464</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.961021482177699</v>
+      </c>
+      <c r="G4" t="n">
+        <v>35.13219036906995</v>
+      </c>
+      <c r="H4" t="n">
+        <v>22.11323101640784</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>33.34668922424316</v>
+        <v>25.09299921989441</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9957603155974105</v>
+        <v>0.9536975256415268</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9972056385643899</v>
+        <v>0.9604850750997985</v>
       </c>
       <c r="G2" t="n">
-        <v>1.041718565298485</v>
+        <v>35.37310208186549</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7294976117107828</v>
+        <v>21.87717418785341</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>39.18174290657043</v>
+        <v>36.17952656745911</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9965907516726771</v>
+        <v>0.9563953673331633</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9972056385643899</v>
+        <v>0.961021482177699</v>
       </c>
       <c r="G3" t="n">
-        <v>1.041718565298485</v>
+        <v>35.13219036906995</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7294976117107828</v>
+        <v>22.11323101640784</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>74.39666152000427</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9581187558108464</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.961021482177699</v>
+      </c>
+      <c r="G4" t="n">
+        <v>35.13219036906995</v>
+      </c>
+      <c r="H4" t="n">
+        <v>22.11323101640784</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>25.09299921989441</v>
+        <v>62.80479264259338</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9536975256415268</v>
+        <v>0.9580611716975916</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9604850750997985</v>
+        <v>0.961021482177699</v>
       </c>
       <c r="G2" t="n">
-        <v>35.37310208186549</v>
+        <v>35.13219036906995</v>
       </c>
       <c r="H2" t="n">
-        <v>21.87717418785341</v>
+        <v>22.11323101640784</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>36.17952656745911</v>
+        <v>80.48120641708374</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9563953673331633</v>
+        <v>0.9591194549184205</v>
       </c>
       <c r="F3" t="n">
-        <v>0.961021482177699</v>
+        <v>0.960585615565733</v>
       </c>
       <c r="G3" t="n">
-        <v>35.13219036906995</v>
+        <v>35.32807234600131</v>
       </c>
       <c r="H3" t="n">
-        <v>22.11323101640784</v>
+        <v>22.57109046746683</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>74.39666152000427</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9581187558108464</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.961021482177699</v>
-      </c>
-      <c r="G4" t="n">
-        <v>35.13219036906995</v>
-      </c>
-      <c r="H4" t="n">
-        <v>22.11323101640784</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 50}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>25.09299921989441</v>
+        <v>62.80479264259338</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9536975256415268</v>
+        <v>0.9580611716975916</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9604850750997985</v>
+        <v>0.961021482177699</v>
       </c>
       <c r="G2" t="n">
-        <v>35.37310208186549</v>
+        <v>35.13219036906995</v>
       </c>
       <c r="H2" t="n">
-        <v>21.87717418785341</v>
+        <v>22.11323101640784</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>36.17952656745911</v>
+        <v>80.48120641708374</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9563953673331633</v>
+        <v>0.9591194549184205</v>
       </c>
       <c r="F3" t="n">
-        <v>0.961021482177699</v>
+        <v>0.960585615565733</v>
       </c>
       <c r="G3" t="n">
-        <v>35.13219036906995</v>
+        <v>35.32807234600131</v>
       </c>
       <c r="H3" t="n">
-        <v>22.11323101640784</v>
+        <v>22.57109046746683</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>74.39666152000427</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9581187558108464</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.961021482177699</v>
-      </c>
-      <c r="G4" t="n">
-        <v>35.13219036906995</v>
-      </c>
-      <c r="H4" t="n">
-        <v>22.11323101640784</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 50}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>62.80479264259338</v>
+        <v>7.138336181640625</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9580611716975916</v>
+        <v>0.9957603155974105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.961021482177699</v>
+        <v>0.9972056385643899</v>
       </c>
       <c r="G2" t="n">
-        <v>35.13219036906995</v>
+        <v>1.041718565298485</v>
       </c>
       <c r="H2" t="n">
-        <v>22.11323101640784</v>
+        <v>0.7294976117107828</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>80.48120641708374</v>
+        <v>6.981253623962402</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9591194549184205</v>
+        <v>0.9965907516726771</v>
       </c>
       <c r="F3" t="n">
-        <v>0.960585615565733</v>
+        <v>0.9972056385643899</v>
       </c>
       <c r="G3" t="n">
-        <v>35.32807234600131</v>
+        <v>1.041718565298485</v>
       </c>
       <c r="H3" t="n">
-        <v>22.57109046746683</v>
+        <v>0.7294976117107828</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 50}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>62.80479264259338</v>
+        <v>7.138336181640625</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9580611716975916</v>
+        <v>0.9957603155974105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.961021482177699</v>
+        <v>0.9972056385643899</v>
       </c>
       <c r="G2" t="n">
-        <v>35.13219036906995</v>
+        <v>1.041718565298485</v>
       </c>
       <c r="H2" t="n">
-        <v>22.11323101640784</v>
+        <v>0.7294976117107828</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>80.48120641708374</v>
+        <v>6.981253623962402</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9591194549184205</v>
+        <v>0.9965907516726771</v>
       </c>
       <c r="F3" t="n">
-        <v>0.960585615565733</v>
+        <v>0.9972056385643899</v>
       </c>
       <c r="G3" t="n">
-        <v>35.32807234600131</v>
+        <v>1.041718565298485</v>
       </c>
       <c r="H3" t="n">
-        <v>22.57109046746683</v>
+        <v>0.7294976117107828</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 50}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.138336181640625</v>
+        <v>9.416287183761597</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9957603155974105</v>
+        <v>0.9959430744288776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9972056385643899</v>
+        <v>0.9971905430163311</v>
       </c>
       <c r="G2" t="n">
-        <v>1.041718565298485</v>
+        <v>1.044528533262776</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7294976117107828</v>
+        <v>0.7230709546390158</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 31}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6.981253623962402</v>
+        <v>10.35789728164673</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9965907516726771</v>
+        <v>0.9967680026539419</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9972056385643899</v>
+        <v>0.9971905430163311</v>
       </c>
       <c r="G3" t="n">
-        <v>1.041718565298485</v>
+        <v>1.044528533262776</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7294976117107828</v>
+        <v>0.7230709546390158</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 31}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.138336181640625</v>
+        <v>9.416287183761597</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9957603155974105</v>
+        <v>0.9959430744288776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9972056385643899</v>
+        <v>0.9971905430163311</v>
       </c>
       <c r="G2" t="n">
-        <v>1.041718565298485</v>
+        <v>1.044528533262776</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7294976117107828</v>
+        <v>0.7230709546390158</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 31}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6.981253623962402</v>
+        <v>10.35789728164673</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9965907516726771</v>
+        <v>0.9967680026539419</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9972056385643899</v>
+        <v>0.9971905430163311</v>
       </c>
       <c r="G3" t="n">
-        <v>1.041718565298485</v>
+        <v>1.044528533262776</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7294976117107828</v>
+        <v>0.7230709546390158</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 31}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>9.416287183761597</v>
+        <v>13.36626982688904</v>
       </c>
       <c r="E2" t="n">
         <v>0.9959430744288776</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>10.35789728164673</v>
+        <v>17.5367443561554</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967680026539419</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>9.416287183761597</v>
+        <v>13.36626982688904</v>
       </c>
       <c r="E2" t="n">
         <v>0.9959430744288776</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>10.35789728164673</v>
+        <v>17.5367443561554</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967680026539419</v>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>13.36626982688904</v>
+        <v>30.65450859069824</v>
       </c>
       <c r="E2" t="n">
         <v>0.9959430744288776</v>
@@ -507,7 +507,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 31}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>17.5367443561554</v>
+        <v>21.15012836456299</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967680026539419</v>
@@ -542,7 +542,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 31}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>13.36626982688904</v>
+        <v>30.65450859069824</v>
       </c>
       <c r="E2" t="n">
         <v>0.9959430744288776</v>
@@ -638,7 +638,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 31}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>17.5367443561554</v>
+        <v>21.15012836456299</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967680026539419</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 31}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>30.65450859069824</v>
+        <v>126.3580760955811</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9959430744288776</v>
+        <v>0.9528316417478734</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9971905430163311</v>
+        <v>0.960381630171073</v>
       </c>
       <c r="G2" t="n">
-        <v>1.044528533262776</v>
+        <v>35.41937290682655</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7230709546390158</v>
+        <v>22.46264210836679</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>21.15012836456299</v>
+        <v>14.1127245426178</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967680026539419</v>
+        <v>0.9563572448117584</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9971905430163311</v>
+        <v>0.960381630171073</v>
       </c>
       <c r="G3" t="n">
-        <v>1.044528533262776</v>
+        <v>35.41937290682655</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7230709546390158</v>
+        <v>22.46264210836679</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>30.65450859069824</v>
+        <v>126.3580760955811</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9959430744288776</v>
+        <v>0.9528316417478734</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9971905430163311</v>
+        <v>0.960381630171073</v>
       </c>
       <c r="G2" t="n">
-        <v>1.044528533262776</v>
+        <v>35.41937290682655</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7230709546390158</v>
+        <v>22.46264210836679</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>21.15012836456299</v>
+        <v>14.1127245426178</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967680026539419</v>
+        <v>0.9563572448117584</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9971905430163311</v>
+        <v>0.960381630171073</v>
       </c>
       <c r="G3" t="n">
-        <v>1.044528533262776</v>
+        <v>35.41937290682655</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7230709546390158</v>
+        <v>22.46264210836679</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>126.3580760955811</v>
+        <v>27.8353750705719</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9528316417478734</v>
+        <v>0.420906216843518</v>
       </c>
       <c r="F2" t="n">
-        <v>0.960381630171073</v>
+        <v>0.515182664165955</v>
       </c>
       <c r="G2" t="n">
-        <v>35.41937290682655</v>
+        <v>0.6127625988621126</v>
       </c>
       <c r="H2" t="n">
-        <v>22.46264210836679</v>
+        <v>0.4577562623078762</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>14.1127245426178</v>
+        <v>66.20461487770081</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9563572448117584</v>
+        <v>0.4558916021332542</v>
       </c>
       <c r="F3" t="n">
-        <v>0.960381630171073</v>
+        <v>0.515182664165955</v>
       </c>
       <c r="G3" t="n">
-        <v>35.41937290682655</v>
+        <v>0.6127625988621126</v>
       </c>
       <c r="H3" t="n">
-        <v>22.46264210836679</v>
+        <v>0.4577562623078762</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>126.3580760955811</v>
+        <v>27.8353750705719</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9528316417478734</v>
+        <v>0.420906216843518</v>
       </c>
       <c r="F2" t="n">
-        <v>0.960381630171073</v>
+        <v>0.515182664165955</v>
       </c>
       <c r="G2" t="n">
-        <v>35.41937290682655</v>
+        <v>0.6127625988621126</v>
       </c>
       <c r="H2" t="n">
-        <v>22.46264210836679</v>
+        <v>0.4577562623078762</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>14.1127245426178</v>
+        <v>66.20461487770081</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9563572448117584</v>
+        <v>0.4558916021332542</v>
       </c>
       <c r="F3" t="n">
-        <v>0.960381630171073</v>
+        <v>0.515182664165955</v>
       </c>
       <c r="G3" t="n">
-        <v>35.41937290682655</v>
+        <v>0.6127625988621126</v>
       </c>
       <c r="H3" t="n">
-        <v>22.46264210836679</v>
+        <v>0.4577562623078762</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>27.8353750705719</v>
+        <v>7.500762224197388</v>
       </c>
       <c r="E2" t="n">
-        <v>0.420906216843518</v>
+        <v>0.4804153325581517</v>
       </c>
       <c r="F2" t="n">
-        <v>0.515182664165955</v>
+        <v>0.5435438726227794</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6127625988621126</v>
+        <v>67.58548695620104</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4577562623078762</v>
+        <v>34.62104164052829</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>66.20461487770081</v>
+        <v>9.164724826812744</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4558916021332542</v>
+        <v>0.5001636848295401</v>
       </c>
       <c r="F3" t="n">
-        <v>0.515182664165955</v>
+        <v>0.5435438726227794</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6127625988621126</v>
+        <v>67.58548695620104</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4577562623078762</v>
+        <v>34.62104164052829</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>27.8353750705719</v>
+        <v>7.500762224197388</v>
       </c>
       <c r="E2" t="n">
-        <v>0.420906216843518</v>
+        <v>0.4804153325581517</v>
       </c>
       <c r="F2" t="n">
-        <v>0.515182664165955</v>
+        <v>0.5435438726227794</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6127625988621126</v>
+        <v>67.58548695620104</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4577562623078762</v>
+        <v>34.62104164052829</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>66.20461487770081</v>
+        <v>9.164724826812744</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4558916021332542</v>
+        <v>0.5001636848295401</v>
       </c>
       <c r="F3" t="n">
-        <v>0.515182664165955</v>
+        <v>0.5435438726227794</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6127625988621126</v>
+        <v>67.58548695620104</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4577562623078762</v>
+        <v>34.62104164052829</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.500762224197388</v>
+        <v>5.712222814559937</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4804153325581517</v>
+        <v>0.9959430744288776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5435438726227794</v>
+        <v>0.9971905430163311</v>
       </c>
       <c r="G2" t="n">
-        <v>67.58548695620104</v>
+        <v>1.044528533262776</v>
       </c>
       <c r="H2" t="n">
-        <v>34.62104164052829</v>
+        <v>0.7230709546390158</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,21 +526,56 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9.164724826812744</v>
+        <v>2.613202571868896</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5001636848295401</v>
+        <v>0.9967680026539419</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5435438726227794</v>
+        <v>0.9971905430163311</v>
       </c>
       <c r="G3" t="n">
-        <v>67.58548695620104</v>
+        <v>1.044528533262776</v>
       </c>
       <c r="H3" t="n">
-        <v>34.62104164052829</v>
+        <v>0.7230709546390158</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.955340147018433</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9969284949233164</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,19 +657,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.500762224197388</v>
+        <v>5.712222814559937</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4804153325581517</v>
+        <v>0.9959430744288776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5435438726227794</v>
+        <v>0.9971905430163311</v>
       </c>
       <c r="G2" t="n">
-        <v>67.58548695620104</v>
+        <v>1.044528533262776</v>
       </c>
       <c r="H2" t="n">
-        <v>34.62104164052829</v>
+        <v>0.7230709546390158</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,21 +692,56 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9.164724826812744</v>
+        <v>2.613202571868896</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5001636848295401</v>
+        <v>0.9967680026539419</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5435438726227794</v>
+        <v>0.9971905430163311</v>
       </c>
       <c r="G3" t="n">
-        <v>67.58548695620104</v>
+        <v>1.044528533262776</v>
       </c>
       <c r="H3" t="n">
-        <v>34.62104164052829</v>
+        <v>0.7230709546390158</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.955340147018433</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9969284949233164</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.712222814559937</v>
+        <v>5.985766887664795</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9959430744288776</v>
+        <v>0.9528316417478734</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9971905430163311</v>
+        <v>0.960381630171073</v>
       </c>
       <c r="G2" t="n">
-        <v>1.044528533262776</v>
+        <v>35.41937290682655</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7230709546390158</v>
+        <v>22.46264210836679</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,56 +526,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.613202571868896</v>
+        <v>5.750111818313599</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967680026539419</v>
+        <v>0.9563572448117584</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9971905430163311</v>
+        <v>0.960381630171073</v>
       </c>
       <c r="G3" t="n">
-        <v>1.044528533262776</v>
+        <v>35.41937290682655</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7230709546390158</v>
+        <v>22.46264210836679</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.955340147018433</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9969284949233164</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9971905430163311</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.044528533262776</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.7230709546390158</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.712222814559937</v>
+        <v>5.985766887664795</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9959430744288776</v>
+        <v>0.9528316417478734</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9971905430163311</v>
+        <v>0.960381630171073</v>
       </c>
       <c r="G2" t="n">
-        <v>1.044528533262776</v>
+        <v>35.41937290682655</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7230709546390158</v>
+        <v>22.46264210836679</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -692,56 +657,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.613202571868896</v>
+        <v>5.750111818313599</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967680026539419</v>
+        <v>0.9563572448117584</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9971905430163311</v>
+        <v>0.960381630171073</v>
       </c>
       <c r="G3" t="n">
-        <v>1.044528533262776</v>
+        <v>35.41937290682655</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7230709546390158</v>
+        <v>22.46264210836679</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.955340147018433</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9969284949233164</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9971905430163311</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.044528533262776</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.7230709546390158</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.985766887664795</v>
+        <v>13.53331780433655</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9528316417478734</v>
+        <v>0.9997793016116973</v>
       </c>
       <c r="F2" t="n">
-        <v>0.960381630171073</v>
+        <v>0.9997917906890258</v>
       </c>
       <c r="G2" t="n">
-        <v>35.41937290682655</v>
+        <v>0.1385222696312019</v>
       </c>
       <c r="H2" t="n">
-        <v>22.46264210836679</v>
+        <v>0.06345873321224887</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.750111818313599</v>
+        <v>19.93512225151062</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9563572448117584</v>
+        <v>0.9997948876301346</v>
       </c>
       <c r="F3" t="n">
-        <v>0.960381630171073</v>
+        <v>0.9997917906890258</v>
       </c>
       <c r="G3" t="n">
-        <v>35.41937290682655</v>
+        <v>0.1385222696312019</v>
       </c>
       <c r="H3" t="n">
-        <v>22.46264210836679</v>
+        <v>0.06345873321224887</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.985766887664795</v>
+        <v>13.53331780433655</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9528316417478734</v>
+        <v>0.9997793016116973</v>
       </c>
       <c r="F2" t="n">
-        <v>0.960381630171073</v>
+        <v>0.9997917906890258</v>
       </c>
       <c r="G2" t="n">
-        <v>35.41937290682655</v>
+        <v>0.1385222696312019</v>
       </c>
       <c r="H2" t="n">
-        <v>22.46264210836679</v>
+        <v>0.06345873321224887</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.750111818313599</v>
+        <v>19.93512225151062</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9563572448117584</v>
+        <v>0.9997948876301346</v>
       </c>
       <c r="F3" t="n">
-        <v>0.960381630171073</v>
+        <v>0.9997917906890258</v>
       </c>
       <c r="G3" t="n">
-        <v>35.41937290682655</v>
+        <v>0.1385222696312019</v>
       </c>
       <c r="H3" t="n">
-        <v>22.46264210836679</v>
+        <v>0.06345873321224887</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>13.53331780433655</v>
+        <v>8.076727867126465</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9997793016116973</v>
+        <v>0.4804153325581517</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9997917906890258</v>
+        <v>0.5435438726227794</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1385222696312019</v>
+        <v>67.58548695620104</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06345873321224887</v>
+        <v>34.62104164052829</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>19.93512225151062</v>
+        <v>9.786618232727051</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9997948876301346</v>
+        <v>0.5001636848295401</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9997917906890258</v>
+        <v>0.5435438726227794</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1385222696312019</v>
+        <v>67.58548695620104</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06345873321224887</v>
+        <v>34.62104164052829</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>13.53331780433655</v>
+        <v>8.076727867126465</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9997793016116973</v>
+        <v>0.4804153325581517</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9997917906890258</v>
+        <v>0.5435438726227794</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1385222696312019</v>
+        <v>67.58548695620104</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06345873321224887</v>
+        <v>34.62104164052829</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>19.93512225151062</v>
+        <v>9.786618232727051</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9997948876301346</v>
+        <v>0.5001636848295401</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9997917906890258</v>
+        <v>0.5435438726227794</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1385222696312019</v>
+        <v>67.58548695620104</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06345873321224887</v>
+        <v>34.62104164052829</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.076727867126465</v>
+        <v>12.90986633300781</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4804153325581517</v>
+        <v>0.914363680035399</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5435438726227794</v>
+        <v>0.9305517581909237</v>
       </c>
       <c r="G2" t="n">
-        <v>67.58548695620104</v>
+        <v>8.940945906678417</v>
       </c>
       <c r="H2" t="n">
-        <v>34.62104164052829</v>
+        <v>5.211787970198956</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9.786618232727051</v>
+        <v>17.80681109428406</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5001636848295401</v>
+        <v>0.9189320204122685</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5435438726227794</v>
+        <v>0.9305517581909237</v>
       </c>
       <c r="G3" t="n">
-        <v>67.58548695620104</v>
+        <v>8.940945906678417</v>
       </c>
       <c r="H3" t="n">
-        <v>34.62104164052829</v>
+        <v>5.211787970198956</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.076727867126465</v>
+        <v>12.90986633300781</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4804153325581517</v>
+        <v>0.914363680035399</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5435438726227794</v>
+        <v>0.9305517581909237</v>
       </c>
       <c r="G2" t="n">
-        <v>67.58548695620104</v>
+        <v>8.940945906678417</v>
       </c>
       <c r="H2" t="n">
-        <v>34.62104164052829</v>
+        <v>5.211787970198956</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9.786618232727051</v>
+        <v>17.80681109428406</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5001636848295401</v>
+        <v>0.9189320204122685</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5435438726227794</v>
+        <v>0.9305517581909237</v>
       </c>
       <c r="G3" t="n">
-        <v>67.58548695620104</v>
+        <v>8.940945906678417</v>
       </c>
       <c r="H3" t="n">
-        <v>34.62104164052829</v>
+        <v>5.211787970198956</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>12.90986633300781</v>
+        <v>31.34100079536438</v>
       </c>
       <c r="E2" t="n">
-        <v>0.914363680035399</v>
+        <v>0.4221265380535599</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9305517581909237</v>
+        <v>0.5242101900276488</v>
       </c>
       <c r="G2" t="n">
-        <v>8.940945906678417</v>
+        <v>0.607030828128258</v>
       </c>
       <c r="H2" t="n">
-        <v>5.211787970198956</v>
+        <v>0.4489069112717186</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 100}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>17.80681109428406</v>
+        <v>33.56432199478149</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9189320204122685</v>
+        <v>0.4569217333243272</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9305517581909237</v>
+        <v>0.5110951993178363</v>
       </c>
       <c r="G3" t="n">
-        <v>8.940945906678417</v>
+        <v>0.6153402589496745</v>
       </c>
       <c r="H3" t="n">
-        <v>5.211787970198956</v>
+        <v>0.4525967415825661</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 50}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>12.90986633300781</v>
+        <v>31.34100079536438</v>
       </c>
       <c r="E2" t="n">
-        <v>0.914363680035399</v>
+        <v>0.4221265380535599</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9305517581909237</v>
+        <v>0.5242101900276488</v>
       </c>
       <c r="G2" t="n">
-        <v>8.940945906678417</v>
+        <v>0.607030828128258</v>
       </c>
       <c r="H2" t="n">
-        <v>5.211787970198956</v>
+        <v>0.4489069112717186</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 100}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>17.80681109428406</v>
+        <v>33.56432199478149</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9189320204122685</v>
+        <v>0.4569217333243272</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9305517581909237</v>
+        <v>0.5110951993178363</v>
       </c>
       <c r="G3" t="n">
-        <v>8.940945906678417</v>
+        <v>0.6153402589496745</v>
       </c>
       <c r="H3" t="n">
-        <v>5.211787970198956</v>
+        <v>0.4525967415825661</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 50}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>31.34100079536438</v>
+        <v>5.089975595474243</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4221265380535599</v>
+        <v>0.9959430744288776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5242101900276488</v>
+        <v>0.9971905430163311</v>
       </c>
       <c r="G2" t="n">
-        <v>0.607030828128258</v>
+        <v>1.044528533262776</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4489069112717186</v>
+        <v>0.7230709546390158</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 100}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>33.56432199478149</v>
+        <v>3.145228624343872</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4569217333243272</v>
+        <v>0.9967680026539419</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5110951993178363</v>
+        <v>0.9971905430163311</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6153402589496745</v>
+        <v>1.044528533262776</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4525967415825661</v>
+        <v>0.7230709546390158</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 50}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.460003137588501</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9969284949233164</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>31.34100079536438</v>
+        <v>5.089975595474243</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4221265380535599</v>
+        <v>0.9959430744288776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5242101900276488</v>
+        <v>0.9971905430163311</v>
       </c>
       <c r="G2" t="n">
-        <v>0.607030828128258</v>
+        <v>1.044528533262776</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4489069112717186</v>
+        <v>0.7230709546390158</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 100}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>33.56432199478149</v>
+        <v>3.145228624343872</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4569217333243272</v>
+        <v>0.9967680026539419</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5110951993178363</v>
+        <v>0.9971905430163311</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6153402589496745</v>
+        <v>1.044528533262776</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4525967415825661</v>
+        <v>0.7230709546390158</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 50}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.460003137588501</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9969284949233164</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.089975595474243</v>
+        <v>4.383365869522095</v>
       </c>
       <c r="E2" t="n">
         <v>0.9959430744288776</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.145228624343872</v>
+        <v>2.543021202087402</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967680026539419</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>6.460003137588501</v>
+        <v>4.431346416473389</v>
       </c>
       <c r="E4" t="n">
         <v>0.9969284949233164</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.089975595474243</v>
+        <v>4.383365869522095</v>
       </c>
       <c r="E2" t="n">
         <v>0.9959430744288776</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.145228624343872</v>
+        <v>2.543021202087402</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967680026539419</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>6.460003137588501</v>
+        <v>4.431346416473389</v>
       </c>
       <c r="E4" t="n">
         <v>0.9969284949233164</v>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.383365869522095</v>
+        <v>26.07546329498291</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9959430744288776</v>
+        <v>0.9384792118700446</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9971905430163311</v>
+        <v>0.9365992887514033</v>
       </c>
       <c r="G2" t="n">
-        <v>1.044528533262776</v>
+        <v>33.58193815324221</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7230709546390158</v>
+        <v>20.61395626552133</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -523,59 +523,24 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>2.543021202087402</v>
+        <v>34.9989058971405</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967680026539419</v>
+        <v>0.9387975117365815</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9971905430163311</v>
+        <v>0.938452982378154</v>
       </c>
       <c r="G3" t="n">
-        <v>1.044528533262776</v>
+        <v>33.0873662758359</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7230709546390158</v>
+        <v>20.64294981605578</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.431346416473389</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9969284949233164</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9971905430163311</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.044528533262776</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.7230709546390158</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.383365869522095</v>
+        <v>26.07546329498291</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9959430744288776</v>
+        <v>0.9384792118700446</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9971905430163311</v>
+        <v>0.9365992887514033</v>
       </c>
       <c r="G2" t="n">
-        <v>1.044528533262776</v>
+        <v>33.58193815324221</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7230709546390158</v>
+        <v>20.61395626552133</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -689,59 +654,24 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>2.543021202087402</v>
+        <v>34.9989058971405</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967680026539419</v>
+        <v>0.9387975117365815</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9971905430163311</v>
+        <v>0.938452982378154</v>
       </c>
       <c r="G3" t="n">
-        <v>1.044528533262776</v>
+        <v>33.0873662758359</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7230709546390158</v>
+        <v>20.64294981605578</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.431346416473389</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9969284949233164</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9971905430163311</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.044528533262776</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.7230709546390158</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>26.07546329498291</v>
+        <v>30.5763635635376</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9384792118700446</v>
+        <v>0.9959430744288776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9365992887514033</v>
+        <v>0.9971905430163311</v>
       </c>
       <c r="G2" t="n">
-        <v>33.58193815324221</v>
+        <v>1.044528533262776</v>
       </c>
       <c r="H2" t="n">
-        <v>20.61395626552133</v>
+        <v>0.7230709546390158</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -523,24 +523,59 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>34.9989058971405</v>
+        <v>16.43288707733154</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9387975117365815</v>
+        <v>0.9967680026539419</v>
       </c>
       <c r="F3" t="n">
-        <v>0.938452982378154</v>
+        <v>0.9971905430163311</v>
       </c>
       <c r="G3" t="n">
-        <v>33.0873662758359</v>
+        <v>1.044528533262776</v>
       </c>
       <c r="H3" t="n">
-        <v>20.64294981605578</v>
+        <v>0.7230709546390158</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>49.61752033233643</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9969284949233164</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,26 +654,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>26.07546329498291</v>
+        <v>30.5763635635376</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9384792118700446</v>
+        <v>0.9959430744288776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9365992887514033</v>
+        <v>0.9971905430163311</v>
       </c>
       <c r="G2" t="n">
-        <v>33.58193815324221</v>
+        <v>1.044528533262776</v>
       </c>
       <c r="H2" t="n">
-        <v>20.61395626552133</v>
+        <v>0.7230709546390158</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -654,24 +689,59 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>34.9989058971405</v>
+        <v>16.43288707733154</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9387975117365815</v>
+        <v>0.9967680026539419</v>
       </c>
       <c r="F3" t="n">
-        <v>0.938452982378154</v>
+        <v>0.9971905430163311</v>
       </c>
       <c r="G3" t="n">
-        <v>33.0873662758359</v>
+        <v>1.044528533262776</v>
       </c>
       <c r="H3" t="n">
-        <v>20.64294981605578</v>
+        <v>0.7230709546390158</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>49.61752033233643</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9969284949233164</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>30.5763635635376</v>
+        <v>12.02220726013184</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9959430744288776</v>
+        <v>0.9998235129695029</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9971905430163311</v>
+        <v>0.9997970644558954</v>
       </c>
       <c r="G2" t="n">
-        <v>1.044528533262776</v>
+        <v>0.1350900964123299</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7230709546390158</v>
+        <v>0.0563297772888775</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>16.43288707733154</v>
+        <v>14.31674456596375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967680026539419</v>
+        <v>0.9998204407468496</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9971905430163311</v>
+        <v>0.9997970644558954</v>
       </c>
       <c r="G3" t="n">
-        <v>1.044528533262776</v>
+        <v>0.1350900964123299</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7230709546390158</v>
+        <v>0.0563297772888775</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>49.61752033233643</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9969284949233164</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9971905430163311</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.044528533262776</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.7230709546390158</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>30.5763635635376</v>
+        <v>12.02220726013184</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9959430744288776</v>
+        <v>0.9998235129695029</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9971905430163311</v>
+        <v>0.9997970644558954</v>
       </c>
       <c r="G2" t="n">
-        <v>1.044528533262776</v>
+        <v>0.1350900964123299</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7230709546390158</v>
+        <v>0.0563297772888775</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>16.43288707733154</v>
+        <v>14.31674456596375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967680026539419</v>
+        <v>0.9998204407468496</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9971905430163311</v>
+        <v>0.9997970644558954</v>
       </c>
       <c r="G3" t="n">
-        <v>1.044528533262776</v>
+        <v>0.1350900964123299</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7230709546390158</v>
+        <v>0.0563297772888775</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>49.61752033233643</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9969284949233164</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9971905430163311</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.044528533262776</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.7230709546390158</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_LightGBM_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>12.02220726013184</v>
+        <v>11.67587733268738</v>
       </c>
       <c r="E2" t="n">
         <v>0.9998235129695029</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>14.31674456596375</v>
+        <v>14.30642175674438</v>
       </c>
       <c r="E3" t="n">
         <v>0.9998204407468496</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>12.02220726013184</v>
+        <v>11.67587733268738</v>
       </c>
       <c r="E2" t="n">
         <v>0.9998235129695029</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>14.31674456596375</v>
+        <v>14.30642175674438</v>
       </c>
       <c r="E3" t="n">
         <v>0.9998204407468496</v>
